--- a/artfynd/A 22043-2025 artfynd.xlsx
+++ b/artfynd/A 22043-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,6 +807,126 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126525622</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98281</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ö Torp, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>589817</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6325529</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vägkant/vägdike</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
